--- a/04_Figures/F05_prediction/WGCNA/responder/c_data/class_source_data.xlsx
+++ b/04_Figures/F05_prediction/WGCNA/responder/c_data/class_source_data.xlsx
@@ -523,7 +523,7 @@
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>0.222857142857143</v>
+        <v>0.219821428571429</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
@@ -558,7 +558,7 @@
         <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>0.211458333333333</v>
+        <v>0.2090625</v>
       </c>
       <c r="K3" t="n">
         <v>1</v>
@@ -581,19 +581,19 @@
         <v>15</v>
       </c>
       <c r="F4" t="n">
-        <v>0.446428571428571</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1259270506167</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.766930092240443</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0.248756218905473</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0.19625</v>
+        <v>0.199553571428571</v>
       </c>
       <c r="K4" t="n">
         <v>1</v>
@@ -616,19 +616,19 @@
         <v>15</v>
       </c>
       <c r="F5" t="n">
-        <v>0.285714285714286</v>
+        <v>0.303571428571429</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00624073984312865</v>
+        <v>0.0164791596570672</v>
       </c>
       <c r="H5" t="n">
-        <v>0.565187831585443</v>
+        <v>0.59066369748579</v>
       </c>
       <c r="I5" t="n">
         <v>0.786069651741294</v>
       </c>
       <c r="J5" t="n">
-        <v>0.450178571428571</v>
+        <v>0.453660714285714</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
@@ -651,19 +651,19 @@
         <v>14</v>
       </c>
       <c r="F6" t="n">
-        <v>0.229166666666667</v>
+        <v>0.270833333333333</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.559741310164942</v>
+        <v>0.607122741397708</v>
       </c>
       <c r="I6" t="n">
-        <v>0.791044776119403</v>
+        <v>0.746268656716418</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4215625</v>
+        <v>0.4203125</v>
       </c>
       <c r="K6" t="n">
         <v>1</v>
@@ -686,19 +686,19 @@
         <v>15</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5</v>
+        <v>0.517857142857143</v>
       </c>
       <c r="G7" t="n">
-        <v>0.162997290658081</v>
+        <v>0.197264635096437</v>
       </c>
       <c r="H7" t="n">
-        <v>0.837002709341919</v>
+        <v>0.838449650617849</v>
       </c>
       <c r="I7" t="n">
-        <v>0.348258706467662</v>
+        <v>0.318407960199005</v>
       </c>
       <c r="J7" t="n">
-        <v>0.407321428571429</v>
+        <v>0.414196428571429</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
@@ -760,7 +760,7 @@
         <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>0.125</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -780,7 +780,7 @@
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>0.857142857142857</v>
       </c>
     </row>
     <row r="5">
@@ -797,7 +797,7 @@
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>0.857142857142857</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -805,16 +805,16 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
         <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -828,7 +828,7 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -848,7 +848,7 @@
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -856,16 +856,16 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
         <v>13</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0.833333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -873,16 +873,16 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
         <v>13</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0.125</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -896,7 +896,7 @@
         <v>13</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -913,10 +913,10 @@
         <v>13</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="E12" t="n">
-        <v>0.142857142857143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -930,10 +930,10 @@
         <v>13</v>
       </c>
       <c r="D13" t="n">
-        <v>0.125</v>
+        <v>0.75</v>
       </c>
       <c r="E13" t="n">
-        <v>0.142857142857143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -947,10 +947,10 @@
         <v>13</v>
       </c>
       <c r="D14" t="n">
-        <v>0.25</v>
+        <v>0.875</v>
       </c>
       <c r="E14" t="n">
-        <v>0.142857142857143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -964,10 +964,10 @@
         <v>13</v>
       </c>
       <c r="D15" t="n">
-        <v>0.375</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>0.142857142857143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -981,7 +981,7 @@
         <v>13</v>
       </c>
       <c r="D16" t="n">
-        <v>0.375</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
         <v>0.285714285714286</v>
@@ -998,10 +998,10 @@
         <v>13</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>0.285714285714286</v>
+        <v>0.428571428571429</v>
       </c>
     </row>
     <row r="18">
@@ -1015,10 +1015,10 @@
         <v>13</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>0.428571428571429</v>
+        <v>0.571428571428571</v>
       </c>
     </row>
     <row r="19">
@@ -1032,10 +1032,10 @@
         <v>13</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>0.571428571428571</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="20">
@@ -1049,10 +1049,10 @@
         <v>13</v>
       </c>
       <c r="D20" t="n">
-        <v>0.625</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>0.571428571428571</v>
+        <v>0.857142857142857</v>
       </c>
     </row>
     <row r="21">
@@ -1066,10 +1066,10 @@
         <v>13</v>
       </c>
       <c r="D21" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>0.571428571428571</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1077,16 +1077,16 @@
         <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C22" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D22" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0.714285714285714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1094,16 +1094,16 @@
         <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C23" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D23" t="n">
-        <v>0.875</v>
+        <v>0.125</v>
       </c>
       <c r="E23" t="n">
-        <v>0.714285714285714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1111,16 +1111,16 @@
         <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C24" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D24" t="n">
-        <v>0.875</v>
+        <v>0.25</v>
       </c>
       <c r="E24" t="n">
-        <v>0.857142857142857</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1128,16 +1128,16 @@
         <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C25" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D25" t="n">
-        <v>0.875</v>
+        <v>0.375</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1145,16 +1145,16 @@
         <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C26" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1168,10 +1168,10 @@
         <v>17</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>0.142857142857143</v>
       </c>
     </row>
     <row r="28">
@@ -1185,10 +1185,10 @@
         <v>17</v>
       </c>
       <c r="D28" t="n">
-        <v>0.125</v>
+        <v>0.5</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>0.285714285714286</v>
       </c>
     </row>
     <row r="29">
@@ -1202,10 +1202,10 @@
         <v>17</v>
       </c>
       <c r="D29" t="n">
-        <v>0.25</v>
+        <v>0.625</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>0.285714285714286</v>
       </c>
     </row>
     <row r="30">
@@ -1219,10 +1219,10 @@
         <v>17</v>
       </c>
       <c r="D30" t="n">
-        <v>0.375</v>
+        <v>0.625</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>0.428571428571429</v>
       </c>
     </row>
     <row r="31">
@@ -1236,10 +1236,10 @@
         <v>17</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5</v>
+        <v>0.625</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>0.571428571428571</v>
       </c>
     </row>
     <row r="32">
@@ -1253,10 +1253,10 @@
         <v>17</v>
       </c>
       <c r="D32" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E32" t="n">
-        <v>0.142857142857143</v>
+        <v>0.571428571428571</v>
       </c>
     </row>
     <row r="33">
@@ -1270,10 +1270,10 @@
         <v>17</v>
       </c>
       <c r="D33" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E33" t="n">
-        <v>0.285714285714286</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="34">
@@ -1287,10 +1287,10 @@
         <v>17</v>
       </c>
       <c r="D34" t="n">
-        <v>0.5</v>
+        <v>0.875</v>
       </c>
       <c r="E34" t="n">
-        <v>0.428571428571429</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="35">
@@ -1304,10 +1304,10 @@
         <v>17</v>
       </c>
       <c r="D35" t="n">
-        <v>0.625</v>
+        <v>0.875</v>
       </c>
       <c r="E35" t="n">
-        <v>0.428571428571429</v>
+        <v>0.857142857142857</v>
       </c>
     </row>
     <row r="36">
@@ -1321,10 +1321,10 @@
         <v>17</v>
       </c>
       <c r="D36" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>0.428571428571429</v>
+        <v>0.857142857142857</v>
       </c>
     </row>
     <row r="37">
@@ -1338,10 +1338,10 @@
         <v>17</v>
       </c>
       <c r="D37" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>0.571428571428571</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -1349,16 +1349,16 @@
         <v>11</v>
       </c>
       <c r="B38" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C38" t="s">
         <v>17</v>
       </c>
       <c r="D38" t="n">
-        <v>0.875</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>0.571428571428571</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1366,16 +1366,16 @@
         <v>11</v>
       </c>
       <c r="B39" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C39" t="s">
         <v>17</v>
       </c>
       <c r="D39" t="n">
-        <v>0.875</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>0.714285714285714</v>
+        <v>0.166666666666667</v>
       </c>
     </row>
     <row r="40">
@@ -1383,16 +1383,16 @@
         <v>11</v>
       </c>
       <c r="B40" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C40" t="s">
         <v>17</v>
       </c>
       <c r="D40" t="n">
-        <v>0.875</v>
+        <v>0.125</v>
       </c>
       <c r="E40" t="n">
-        <v>0.857142857142857</v>
+        <v>0.166666666666667</v>
       </c>
     </row>
     <row r="41">
@@ -1400,16 +1400,16 @@
         <v>11</v>
       </c>
       <c r="B41" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C41" t="s">
         <v>17</v>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="E41" t="n">
-        <v>0.857142857142857</v>
+        <v>0.166666666666667</v>
       </c>
     </row>
     <row r="42">
@@ -1417,16 +1417,16 @@
         <v>11</v>
       </c>
       <c r="B42" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C42" t="s">
         <v>17</v>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>0.375</v>
       </c>
       <c r="E42" t="n">
-        <v>1</v>
+        <v>0.166666666666667</v>
       </c>
     </row>
     <row r="43">
@@ -1440,10 +1440,10 @@
         <v>17</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>0.166666666666667</v>
       </c>
     </row>
     <row r="44">
@@ -1457,10 +1457,10 @@
         <v>17</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E44" t="n">
-        <v>0.166666666666667</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="45">
@@ -1474,10 +1474,10 @@
         <v>17</v>
       </c>
       <c r="D45" t="n">
-        <v>0.125</v>
+        <v>0.625</v>
       </c>
       <c r="E45" t="n">
-        <v>0.166666666666667</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="46">
@@ -1491,10 +1491,10 @@
         <v>17</v>
       </c>
       <c r="D46" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="E46" t="n">
-        <v>0.166666666666667</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="47">
@@ -1508,10 +1508,10 @@
         <v>17</v>
       </c>
       <c r="D47" t="n">
-        <v>0.375</v>
+        <v>0.875</v>
       </c>
       <c r="E47" t="n">
-        <v>0.166666666666667</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="48">
@@ -1525,10 +1525,10 @@
         <v>17</v>
       </c>
       <c r="D48" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="E48" t="n">
         <v>0.5</v>
-      </c>
-      <c r="E48" t="n">
-        <v>0.166666666666667</v>
       </c>
     </row>
     <row r="49">
@@ -1542,10 +1542,10 @@
         <v>17</v>
       </c>
       <c r="D49" t="n">
-        <v>0.625</v>
+        <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>0.166666666666667</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="50">
@@ -1559,10 +1559,10 @@
         <v>17</v>
       </c>
       <c r="D50" t="n">
-        <v>0.625</v>
+        <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>0.333333333333333</v>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="51">
@@ -1576,10 +1576,10 @@
         <v>17</v>
       </c>
       <c r="D51" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>0.333333333333333</v>
+        <v>0.833333333333333</v>
       </c>
     </row>
     <row r="52">
@@ -1593,10 +1593,10 @@
         <v>17</v>
       </c>
       <c r="D52" t="n">
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>0.333333333333333</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -1604,16 +1604,16 @@
         <v>11</v>
       </c>
       <c r="B53" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C53" t="s">
         <v>17</v>
       </c>
       <c r="D53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>0.333333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -1621,16 +1621,16 @@
         <v>11</v>
       </c>
       <c r="B54" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C54" t="s">
         <v>17</v>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>0.5</v>
+        <v>0.142857142857143</v>
       </c>
     </row>
     <row r="55">
@@ -1638,16 +1638,16 @@
         <v>11</v>
       </c>
       <c r="B55" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C55" t="s">
         <v>17</v>
       </c>
       <c r="D55" t="n">
-        <v>1</v>
+        <v>0.125</v>
       </c>
       <c r="E55" t="n">
-        <v>0.666666666666667</v>
+        <v>0.142857142857143</v>
       </c>
     </row>
     <row r="56">
@@ -1655,16 +1655,16 @@
         <v>11</v>
       </c>
       <c r="B56" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C56" t="s">
         <v>17</v>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="E56" t="n">
-        <v>0.833333333333333</v>
+        <v>0.142857142857143</v>
       </c>
     </row>
     <row r="57">
@@ -1672,16 +1672,16 @@
         <v>11</v>
       </c>
       <c r="B57" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C57" t="s">
         <v>17</v>
       </c>
       <c r="D57" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>0.285714285714286</v>
       </c>
     </row>
     <row r="58">
@@ -1695,10 +1695,10 @@
         <v>17</v>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>0.285714285714286</v>
       </c>
     </row>
     <row r="59">
@@ -1712,10 +1712,10 @@
         <v>17</v>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="E59" t="n">
-        <v>0.142857142857143</v>
+        <v>0.428571428571429</v>
       </c>
     </row>
     <row r="60">
@@ -1729,10 +1729,10 @@
         <v>17</v>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E60" t="n">
-        <v>0.285714285714286</v>
+        <v>0.428571428571429</v>
       </c>
     </row>
     <row r="61">
@@ -1746,10 +1746,10 @@
         <v>17</v>
       </c>
       <c r="D61" t="n">
-        <v>0.125</v>
+        <v>0.5</v>
       </c>
       <c r="E61" t="n">
-        <v>0.285714285714286</v>
+        <v>0.571428571428571</v>
       </c>
     </row>
     <row r="62">
@@ -1763,10 +1763,10 @@
         <v>17</v>
       </c>
       <c r="D62" t="n">
-        <v>0.25</v>
+        <v>0.625</v>
       </c>
       <c r="E62" t="n">
-        <v>0.285714285714286</v>
+        <v>0.571428571428571</v>
       </c>
     </row>
     <row r="63">
@@ -1780,10 +1780,10 @@
         <v>17</v>
       </c>
       <c r="D63" t="n">
-        <v>0.375</v>
+        <v>0.75</v>
       </c>
       <c r="E63" t="n">
-        <v>0.285714285714286</v>
+        <v>0.571428571428571</v>
       </c>
     </row>
     <row r="64">
@@ -1797,10 +1797,10 @@
         <v>17</v>
       </c>
       <c r="D64" t="n">
-        <v>0.375</v>
+        <v>0.75</v>
       </c>
       <c r="E64" t="n">
-        <v>0.428571428571429</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="65">
@@ -1814,10 +1814,10 @@
         <v>17</v>
       </c>
       <c r="D65" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E65" t="n">
-        <v>0.428571428571429</v>
+        <v>0.857142857142857</v>
       </c>
     </row>
     <row r="66">
@@ -1831,10 +1831,10 @@
         <v>17</v>
       </c>
       <c r="D66" t="n">
-        <v>0.625</v>
+        <v>0.75</v>
       </c>
       <c r="E66" t="n">
-        <v>0.428571428571429</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -1848,10 +1848,10 @@
         <v>17</v>
       </c>
       <c r="D67" t="n">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="E67" t="n">
-        <v>0.428571428571429</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -1865,94 +1865,9 @@
         <v>17</v>
       </c>
       <c r="D68" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>0.571428571428571</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s">
-        <v>11</v>
-      </c>
-      <c r="B69" t="s">
-        <v>16</v>
-      </c>
-      <c r="C69" t="s">
-        <v>17</v>
-      </c>
-      <c r="D69" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E69" t="n">
-        <v>0.714285714285714</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s">
-        <v>11</v>
-      </c>
-      <c r="B70" t="s">
-        <v>16</v>
-      </c>
-      <c r="C70" t="s">
-        <v>17</v>
-      </c>
-      <c r="D70" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E70" t="n">
-        <v>0.857142857142857</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s">
-        <v>11</v>
-      </c>
-      <c r="B71" t="s">
-        <v>16</v>
-      </c>
-      <c r="C71" t="s">
-        <v>17</v>
-      </c>
-      <c r="D71" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="E71" t="n">
-        <v>0.857142857142857</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s">
-        <v>11</v>
-      </c>
-      <c r="B72" t="s">
-        <v>16</v>
-      </c>
-      <c r="C72" t="s">
-        <v>17</v>
-      </c>
-      <c r="D72" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="E72" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s">
-        <v>11</v>
-      </c>
-      <c r="B73" t="s">
-        <v>16</v>
-      </c>
-      <c r="C73" t="s">
-        <v>17</v>
-      </c>
-      <c r="D73" t="n">
-        <v>1</v>
-      </c>
-      <c r="E73" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2004,7 +1919,7 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.221874576793134</v>
+        <v>0.168995569971987</v>
       </c>
     </row>
     <row r="3">
@@ -2144,7 +2059,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.571694203501768</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="10">
@@ -2344,7 +2259,7 @@
         <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>0.00466184289237881</v>
+        <v>0.384615384615385</v>
       </c>
     </row>
     <row r="20">
@@ -2584,7 +2499,7 @@
         <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>0.55638796089309</v>
+        <v>0.428571428571429</v>
       </c>
     </row>
     <row r="32">
@@ -2604,7 +2519,7 @@
         <v>1</v>
       </c>
       <c r="F32" t="n">
-        <v>0.437372163292947</v>
+        <v>0.377383653438212</v>
       </c>
     </row>
     <row r="33">
@@ -2624,7 +2539,7 @@
         <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>0.228054718945456</v>
+        <v>0.351345115882008</v>
       </c>
     </row>
     <row r="34">
@@ -2644,7 +2559,7 @@
         <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>0.199657235201874</v>
+        <v>0.350158485030713</v>
       </c>
     </row>
     <row r="35">
@@ -2664,7 +2579,7 @@
         <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>0.999485189442865</v>
+        <v>0.428571428571429</v>
       </c>
     </row>
     <row r="36">
@@ -2684,7 +2599,7 @@
         <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>0.4883185020069</v>
+        <v>0.409880915312207</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2619,7 @@
         <v>1</v>
       </c>
       <c r="F37" t="n">
-        <v>0.317363320173127</v>
+        <v>0.312248014399911</v>
       </c>
     </row>
     <row r="38">
@@ -2724,7 +2639,7 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0.685554432919685</v>
+        <v>0.563347316640877</v>
       </c>
     </row>
     <row r="39">
@@ -2744,7 +2659,7 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0.310610005838009</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="40">
@@ -2764,7 +2679,7 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>0.716735902123315</v>
+        <v>0.494920432709689</v>
       </c>
     </row>
     <row r="41">
@@ -2784,7 +2699,7 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0.405053760309764</v>
+        <v>0.494909922633856</v>
       </c>
     </row>
     <row r="42">
@@ -2804,7 +2719,7 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0.82838125192804</v>
+        <v>0.974016601203786</v>
       </c>
     </row>
     <row r="43">
@@ -2824,7 +2739,7 @@
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0.0653391341074157</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="44">
@@ -2844,7 +2759,7 @@
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0.508419423235261</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="45">
@@ -2864,7 +2779,7 @@
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0.392028999053907</v>
+        <v>0.576317578848637</v>
       </c>
     </row>
     <row r="46">
@@ -2884,7 +2799,7 @@
         <v>1</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.218311970082758</v>
+        <v>-0.376565022704002</v>
       </c>
     </row>
     <row r="47">
@@ -2904,7 +2819,7 @@
         <v>1</v>
       </c>
       <c r="F47" t="n">
-        <v>0.356624965652779</v>
+        <v>0.270211159277124</v>
       </c>
     </row>
     <row r="48">
@@ -2924,7 +2839,7 @@
         <v>1</v>
       </c>
       <c r="F48" t="n">
-        <v>0.234926581018256</v>
+        <v>0.523802224526056</v>
       </c>
     </row>
     <row r="49">
@@ -2944,7 +2859,7 @@
         <v>1</v>
       </c>
       <c r="F49" t="n">
-        <v>0.542799097801842</v>
+        <v>0.560373657230879</v>
       </c>
     </row>
     <row r="50">
@@ -2964,7 +2879,7 @@
         <v>1</v>
       </c>
       <c r="F50" t="n">
-        <v>0.299995972080984</v>
+        <v>0.380602046428024</v>
       </c>
     </row>
     <row r="51">
@@ -2984,7 +2899,7 @@
         <v>1</v>
       </c>
       <c r="F51" t="n">
-        <v>0.283683377097918</v>
+        <v>0.364504744937164</v>
       </c>
     </row>
     <row r="52">
@@ -3004,7 +2919,7 @@
         <v>1</v>
       </c>
       <c r="F52" t="n">
-        <v>0.492164802976348</v>
+        <v>0.392015782395836</v>
       </c>
     </row>
     <row r="53">
@@ -3024,7 +2939,7 @@
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>1.10740663938852</v>
+        <v>1.0600464364485</v>
       </c>
     </row>
     <row r="54">
@@ -3044,7 +2959,7 @@
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>0.294795027698148</v>
+        <v>0.447755237179222</v>
       </c>
     </row>
     <row r="55">
@@ -3064,7 +2979,7 @@
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>0.332219304817828</v>
+        <v>0.322279275552308</v>
       </c>
     </row>
     <row r="56">
@@ -3084,7 +2999,7 @@
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>0.169251573472736</v>
+        <v>0.111248774782425</v>
       </c>
     </row>
     <row r="57">
@@ -3104,7 +3019,7 @@
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>0.864752950574324</v>
+        <v>0.860922525337232</v>
       </c>
     </row>
     <row r="58">
@@ -3124,7 +3039,7 @@
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>0.588767320371319</v>
+        <v>0.627318536197047</v>
       </c>
     </row>
     <row r="59">
@@ -3144,7 +3059,7 @@
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>0.938944719360965</v>
+        <v>0.811612283439909</v>
       </c>
     </row>
     <row r="60">
@@ -3164,7 +3079,7 @@
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>0.312787777828263</v>
+        <v>0.368205856937067</v>
       </c>
     </row>
     <row r="61">
@@ -3184,7 +3099,7 @@
         <v>1</v>
       </c>
       <c r="F61" t="n">
-        <v>0.461401708089966</v>
+        <v>0.42567400545509</v>
       </c>
     </row>
     <row r="62">
@@ -3204,7 +3119,7 @@
         <v>1</v>
       </c>
       <c r="F62" t="n">
-        <v>0.15503117850195</v>
+        <v>0.143637807468746</v>
       </c>
     </row>
     <row r="63">
@@ -3224,7 +3139,7 @@
         <v>1</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.126133644458528</v>
+        <v>0.257074211665518</v>
       </c>
     </row>
     <row r="64">
@@ -3244,7 +3159,7 @@
         <v>1</v>
       </c>
       <c r="F64" t="n">
-        <v>0.96160959270016</v>
+        <v>1.00723295892525</v>
       </c>
     </row>
     <row r="65">
@@ -3264,7 +3179,7 @@
         <v>1</v>
       </c>
       <c r="F65" t="n">
-        <v>0.0601869118313867</v>
+        <v>0.0928601060579579</v>
       </c>
     </row>
     <row r="66">
@@ -3284,7 +3199,7 @@
         <v>1</v>
       </c>
       <c r="F66" t="n">
-        <v>0.208277101719729</v>
+        <v>0.311527926673897</v>
       </c>
     </row>
     <row r="67">
@@ -3304,7 +3219,7 @@
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>0.683732547732776</v>
+        <v>0.695980069125311</v>
       </c>
     </row>
     <row r="68">
@@ -3324,7 +3239,7 @@
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>0.28131750027361</v>
+        <v>0.277893343514561</v>
       </c>
     </row>
     <row r="69">
@@ -3344,7 +3259,7 @@
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>0.520531581910127</v>
+        <v>0.35859879983519</v>
       </c>
     </row>
     <row r="70">
@@ -3364,7 +3279,7 @@
         <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>0.41545446512793</v>
+        <v>0.413471744378833</v>
       </c>
     </row>
     <row r="71">
@@ -3384,7 +3299,7 @@
         <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>0.857390016777123</v>
+        <v>0.78164219058644</v>
       </c>
     </row>
     <row r="72">
@@ -3404,7 +3319,7 @@
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>0.423286103790334</v>
+        <v>0.413239761257579</v>
       </c>
     </row>
     <row r="73">
@@ -3424,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>0.676512863762838</v>
+        <v>0.64007758927576</v>
       </c>
     </row>
     <row r="74">
@@ -3444,7 +3359,7 @@
         <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>0.658080307197877</v>
+        <v>0.646164792359039</v>
       </c>
     </row>
     <row r="75">
@@ -3464,7 +3379,7 @@
         <v>1</v>
       </c>
       <c r="F75" t="n">
-        <v>0.654063641724902</v>
+        <v>0.633391364196755</v>
       </c>
     </row>
     <row r="76">
@@ -3484,7 +3399,7 @@
         <v>1</v>
       </c>
       <c r="F76" t="n">
-        <v>0.440592442347672</v>
+        <v>0.471948551578843</v>
       </c>
     </row>
     <row r="77">
@@ -3504,7 +3419,7 @@
         <v>1</v>
       </c>
       <c r="F77" t="n">
-        <v>0.355303174715</v>
+        <v>0.327413251181893</v>
       </c>
     </row>
     <row r="78">
@@ -3524,7 +3439,7 @@
         <v>1</v>
       </c>
       <c r="F78" t="n">
-        <v>0.325423426916164</v>
+        <v>0.413762746817548</v>
       </c>
     </row>
     <row r="79">
@@ -3544,7 +3459,7 @@
         <v>1</v>
       </c>
       <c r="F79" t="n">
-        <v>2.28417492628299</v>
+        <v>1.98010048255334</v>
       </c>
     </row>
     <row r="80">
@@ -3564,7 +3479,7 @@
         <v>1</v>
       </c>
       <c r="F80" t="n">
-        <v>0.343804395577271</v>
+        <v>0.30908033274636</v>
       </c>
     </row>
     <row r="81">
@@ -3584,7 +3499,7 @@
         <v>1</v>
       </c>
       <c r="F81" t="n">
-        <v>0.215409376601159</v>
+        <v>0.195306090384608</v>
       </c>
     </row>
     <row r="82">
@@ -3604,7 +3519,7 @@
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>0.548940363080038</v>
+        <v>0.611863523059278</v>
       </c>
     </row>
     <row r="83">
@@ -3624,7 +3539,7 @@
         <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>0.323352837604661</v>
+        <v>0.182728774110802</v>
       </c>
     </row>
     <row r="84">
@@ -3644,7 +3559,7 @@
         <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>0.559779505762346</v>
+        <v>0.468964105605342</v>
       </c>
     </row>
     <row r="85">
@@ -3664,7 +3579,7 @@
         <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>0.356808157848069</v>
+        <v>0.338022503767513</v>
       </c>
     </row>
     <row r="86">
@@ -3684,7 +3599,7 @@
         <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>0.535201677866887</v>
+        <v>0.76988713430009</v>
       </c>
     </row>
     <row r="87">
@@ -3704,7 +3619,7 @@
         <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>0.0875321750600103</v>
+        <v>0.0235913527688197</v>
       </c>
     </row>
     <row r="88">
@@ -3724,7 +3639,7 @@
         <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>0.410406057025939</v>
+        <v>0.344275909519947</v>
       </c>
     </row>
     <row r="89">
@@ -3744,7 +3659,7 @@
         <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>0.39801239782965</v>
+        <v>0.633918243752608</v>
       </c>
     </row>
   </sheetData>
